--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="250">
   <si>
     <t>Наименование</t>
   </si>
@@ -47,20 +47,6 @@
   </si>
   <si>
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/1c34e480-47cf-46f3-aa7a-a917803216bc</t>
-  </si>
-  <si>
-    <t>Пиво 4Brewers Emergency Exit</t>
-  </si>
-  <si>
-    <t>Х1861</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/5391a18f-2bfc-4995-bb45-616522b435af
- https://online.sbis.ru/fs-public/ekt_files/42ddb14a-ad16-4552-b683-3f124c7cfa9e</t>
-  </si>
-  <si>
-    <t>10% ABV IPA - Quadruple 100 IBU
-Плотный, насыщенный светлый эль. Средний чистый солодовый характер, высокая хмелевая горечь и яркий аромат цитрусов, хвои и тропических фруктов.</t>
   </si>
   <si>
     <t>Пиво 4Brewers Giraffe Milk 0.45</t>
@@ -91,32 +77,18 @@
 Cветлый полнотелый эль с явной, но ненавязчивой горечью и цитрусово- хвойным ароматом хмелей El Dorado, Centennial и Cascade.</t>
   </si>
   <si>
-    <t>Пиво 4Brewers Грибы судьбы</t>
-  </si>
-  <si>
-    <t>Х2264</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/0fda689f-911d-4b71-b5f6-8e20dd3ac789
- https://online.sbis.ru/fs-public/ekt_files/019e918e-d0eb-7256-873d-be3a1efb7dd5</t>
-  </si>
-  <si>
-    <t>5% ABV Sour - Other Gose
-Насыщенный светлый кислый эль. Яркий и насыщенный вкус умеренно солёного грибного супа. Выраженный аромат базилика и кориандра.</t>
-  </si>
-  <si>
-    <t>Пиво 4Brewers Доза Orange Pulp + Mango + Pineapple</t>
-  </si>
-  <si>
-    <t>Х2229</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/2c5b36af-c1ad-4d39-8ae4-0f3dba42167a
- https://online.sbis.ru/fs-public/ekt_files/355c4749-4dd4-4ae9-9b43-4c3d90bba111</t>
-  </si>
-  <si>
-    <t>6% ABV Sour - Smoothie / Pastry 6 IBU
-Густой насыщенный кислый эль. Яркий аромат и вкус манго, ананаса и апельсина, умеренная кислотность и консистенция смузи.</t>
+    <t>Пиво 4Brewers Даркнет</t>
+  </si>
+  <si>
+    <t>Х2275</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/78dcce86-6bc3-4b3e-9fa4-cc33ce1c6913
+ https://online.sbis.ru/fs-public/ekt_files/8b3bf58a-5845-47e9-bfaa-18b22666b3e8</t>
+  </si>
+  <si>
+    <t>6.9% ABV Stout - Other
+Тёмный насыщенный эль. Умеренно сладкий, жареный солодовый вкус с тонами шоколада дополняет яркий аромат и вкус кокоса. И всё это в густой тягучей банановой текстуре смузи.</t>
   </si>
   <si>
     <t>Пиво 4Brewers Доза Банан Черника 0.45</t>
@@ -133,20 +105,6 @@
 Густой насыщенный кислый эль. Яркий бананово-черничный аромат и вкус, умеренная кислотность и консистенция смузи.</t>
   </si>
   <si>
-    <t>Пиво 4Brewers Доза Манго Малина</t>
-  </si>
-  <si>
-    <t>Х2230</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/b2879d17-eb0f-4116-ba28-49e32b1b7b82
- https://online.sbis.ru/fs-public/ekt_files/203e09b6-6a4b-4399-87c5-e826f0a1320b</t>
-  </si>
-  <si>
-    <t>Sour - Smoothie / Pastry 6% ABV
-Густой насыщенный кислый эль. Яркий аромат и вкус манго и малины, умеренная кислотность и консистенция смузи.</t>
-  </si>
-  <si>
     <t>Пиво 4Brewers Зависимость 0,45</t>
   </si>
   <si>
@@ -161,32 +119,18 @@
 Лёгкий светлый кислый эль. Насыщенный, сочный томатный вкус, чуть соли, немного базилика и кориандра, и капелька пряной паприки.</t>
   </si>
   <si>
-    <t>Пиво 4Brewers Острая Зависимость 0.45</t>
-  </si>
-  <si>
-    <t>Х2244</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/a3d1a265-eaab-4c7c-8774-0fa0a7851e57
- https://online.sbis.ru/fs-public/ekt_files/019f3ba0-e98c-7f98-b54e-c3247a1ae5cc</t>
-  </si>
-  <si>
-    <t>6.9% ABV Sour - Tomato / Vegetable Gose
-Насыщенный светлый кислый эль. Сочный томатный вкус, копчёный солод, чуть соли, немного базилика, кориандр, копчёная паприка и острый перец чили.</t>
-  </si>
-  <si>
-    <t>Пиво 4Brewers Похищение человеков инопланетянами</t>
-  </si>
-  <si>
-    <t>Х2233</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/bd63e062-4f47-468b-a3f1-873acd328d94
- https://online.sbis.ru/fs-public/ekt_files/d163d8d8-08b6-4cb0-81f1-c12abcc413a0</t>
-  </si>
-  <si>
-    <t>7.5% ABV IPA - White / Wheat 67 IBU
-Белый IPA — светлый эль. Яркий цитрусовый аромат и мягкий пшеничный вкус, балансирующий хмелевую горечь, делают этот сорт насыщенным, но при этом очень питким. Однако будьте внимательны, пиво кажется куда менее крепким, чем есть на самом деле.</t>
+    <t>Пиво 4Brewers Заготовка</t>
+  </si>
+  <si>
+    <t>Х2274</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/591d30d0-ac54-46b2-aadc-8ba5129b09c5
+ https://online.sbis.ru/fs-public/ekt_files/f6ae4a1e-c50d-4ed3-bf9d-887a9ca561e8</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Tomato / Vegetable Gose
+Насыщенный кислый и прозрачный эль. Сочная томатная база, немного соли и выраженные ноты кориандра, лаврового листа, базилика, паприки и чеснока.</t>
   </si>
   <si>
     <t>Пиво BAD Груша Блю Чиз</t>
@@ -217,20 +161,6 @@
 Хруст печенья, сочность апельсина и бархат шоколада разожгут страсть в каждом глотке этого чувственного смузи саур эль.</t>
   </si>
   <si>
-    <t>Пиво Magic Mess Нумерология</t>
-  </si>
-  <si>
-    <t>Х2242</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d41616e0-40e1-4661-9dbc-5e8a47d1f8d6
- https://online.sbis.ru/fs-public/ekt_files/3b55537a-11a3-497b-bf43-1757c5241185</t>
-  </si>
-  <si>
-    <t>5.5% ABV Sour - Fruited
-Не боись, мы все посчитали по натальной карте и хьюман дизайну. #манго в асценденте, #ананас и #киви в 7-м доме. Даже не думай спорить со звездами, попробовать этот #sourale - твой кармический долг.</t>
-  </si>
-  <si>
     <t>Пиво Доза [Blackcurrant + Strawberry + Cranberry + Raspberry + Cherry + Cowberry]</t>
   </si>
   <si>
@@ -251,19 +181,6 @@
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d7ede847-6816-4fec-876d-5d8590960aa5</t>
   </si>
   <si>
-    <t>Пиво BAD MOUSSE WITH GUAVA AND PINEAPPLE</t>
-  </si>
-  <si>
-    <t>Х2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/bb362a20-ddbf-474a-8497-f4ccbe9bb196</t>
-  </si>
-  <si>
-    <t>5.5% ABV Sour Smoothie
-Сочная, сладкая гуава, с ее неповторимым ароматом, который манит и интригует, словно далекий, манящий остров. И, конечно, ананасовый сок – солнечный, искрящийся, полный жизни и энергии!</t>
-  </si>
-  <si>
     <t>Пиво BAD WAFFLE WITH MELON  AND BANANA</t>
   </si>
   <si>
@@ -297,36 +214,6 @@
   <si>
     <t>6.9% ABV IPA - New England / Hazy
 Это сочный New England IPA, сваренный с использованием дрожжей Pomona и засыпью хмелей Citra, Citra Cryo и Krush.</t>
-  </si>
-  <si>
-    <t>Пиво Big Pot Шарик желтый</t>
-  </si>
-  <si>
-    <t>Х2260</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/b91f01d3-d8e6-4799-94fa-d6fbd96f5627
- https://online.sbis.ru/fs-public/ekt_files/019f45fa-e609-7e55-8e42-3c1e9966f42b</t>
-  </si>
-  <si>
-    <t>6.5% ABV Sour - Smoothie / Pastry
-Смузи со вкусом лимонного мороженого с анансом. Наша новая линейка летних смузи с большим количеством фруктов, молочным сахаром и ванилью.
-Пейте холодным.</t>
-  </si>
-  <si>
-    <t>Пиво Big Pot Шарик Красный</t>
-  </si>
-  <si>
-    <t>Х2259</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/eb475f0e-0f24-41e9-b025-970ec9586992
- https://online.sbis.ru/fs-public/ekt_files/019f7ea7-748d-7557-84ad-f1f14e9d0e33</t>
-  </si>
-  <si>
-    <t>6.5% ABV Sour - Smoothie / Pastry
-Наша вариация клубничного мороженного с малиной. Старший брат Шарика , приуроченного к Lobotomy 2026, отличающийся лишь более высоким градусом.
-Пейте холодным.</t>
   </si>
   <si>
     <t>Пиво Big Pot Шарик смородина</t>
@@ -347,56 +234,17 @@
 авиаклуб ОСОАВИАХИМа.</t>
   </si>
   <si>
-    <t>Пиво Hangar Винговер</t>
-  </si>
-  <si>
-    <t>Х2072</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/b71ffac8-8047-43a2-8286-545b9a551ee7</t>
-  </si>
-  <si>
-    <t>ABV 4.5% Pale Ale
-Классический английский эль с насыщенной палитрой, где солодовые ноты светлого и карамельного ячменя взмывают вверх, совершая маневр высшего пилотажа в чистом небе.</t>
-  </si>
-  <si>
-    <t>Пиво Hangar Жар-Птица</t>
-  </si>
-  <si>
-    <t>Х2073</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d0271ac3-00da-4afd-976f-77608485eae1</t>
-  </si>
-  <si>
-    <t>ABV 5.0% Amber Ale
-Насыщенный и теплый, с бархатистой солодовой сладостью и яркими карамельными отблесками, словно закатное солнце на крыльях знаменитого биплана.</t>
-  </si>
-  <si>
-    <t>Пиво Hangar Ночная Ведьма</t>
-  </si>
-  <si>
-    <t>Х2075</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/ac78d2fc-ea31-4873-8136-e4bd71fc4735</t>
-  </si>
-  <si>
-    <t>ABV 4.0% Milk Stout
-Жженый и карамельный солод создают насыщенный букет вкуса, а лактоза придает мягкую молочную кремовость – как слегка заметный след самолета в ночном небе.</t>
-  </si>
-  <si>
-    <t>Пиво Hangar Поцелуй Стюардессы</t>
-  </si>
-  <si>
-    <t>Х2077</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/0d2ca958-da9e-491b-8a41-6d00437285fd</t>
-  </si>
-  <si>
-    <t>ABV 3.6% Pilsner
-Классика европейской школы с воздушным драйвом. Мягкий и освежающий, он раскрывается солодовой сладостью и легкой карамелью.</t>
+    <t>Пиво Hangar Полет Шмеля</t>
+  </si>
+  <si>
+    <t>Х2076</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d2ea8f52-b394-451b-bbc2-6a520732e6a2</t>
+  </si>
+  <si>
+    <t>ABV 5.5% APA
+Плотный и насыщенный, он сочетает в себе мягкие солодовые оттенки светлого и карамельного ячменя с тонкой, но выразительной хмелевой горчинкой – как точные приборы и мощные двигатели, обеспечивающие стабильность полета.</t>
   </si>
   <si>
     <t>Jaws</t>
@@ -514,20 +362,6 @@
 "Пробили стаут вместо саура? Гааааля, у нас отмеееееена! Учини скандал и требуй администратора, ведь не только ты хочешь #buy_it. Сочный манговый саур, плотный, как очередь на кассу, с кислинкой грейпфрута и свежим ананасовым послевкусием просто обязан упасть в твою пивную корзинку.</t>
   </si>
   <si>
-    <t>Пиво Magic Mess Галя, у нас отмена 0.45</t>
-  </si>
-  <si>
-    <t>Х1821</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/456de07d-2a25-400a-bc8d-de93f9045085
- https://online.sbis.ru/fs-public/ekt_files/69d5d985-3c61-4a0c-ae6d-cc562c3ef16d</t>
-  </si>
-  <si>
-    <t>5.5% ABV Sour - Fruited N/A IBU
-Пробили стаут вместо саура? Гааааля, у нас отмеееееена! Учини скандал и требуй администратора, ведь не только ты хочешь #buy_it. Сочный манговый саур, плотный, как очередь на кассу, с кислинкой грейпфрута и свежим ананасовым послевкусием просто обязан упасть в твою пивную корзинку.</t>
-  </si>
-  <si>
     <t>Panzer Brewery</t>
   </si>
   <si>
@@ -547,93 +381,10 @@
 Мексиканская интерпретация нашего томатного гозе Catch Up - всё та же пряная томатная основа, дополненная пастой перца чили и соком лайма.</t>
   </si>
   <si>
-    <t>Пиво Panzer Темпера HBC 630 Mosaic</t>
-  </si>
-  <si>
-    <t>Х2234</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/17f6ad20-ea10-4cec-ae16-fcf4c484d613</t>
-  </si>
-  <si>
-    <t>6.5% ABV IPA - New England / Hazy 39 IBU
-Cухой, душистый New England IPA, который продолжает экспериментальную линейку "Темпера", посвященную охмелённым сортам.</t>
-  </si>
-  <si>
     <t>Saldens</t>
   </si>
   <si>
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d4e7177f-3ee7-40b4-9481-8bad8d920f59</t>
-  </si>
-  <si>
-    <t>Пиво Saldens American 4C AIPA</t>
-  </si>
-  <si>
-    <t>Х1864</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/ed0780ee-6da8-4d10-9b56-29fd797c6da4
- https://online.sbis.ru/fs-public/ekt_files/a930522b-c319-40e2-9376-73c87eb2c5c4</t>
-  </si>
-  <si>
-    <t>7% ABV 60 IBU IPA - American
-Dry Hop: Centennial, Chinook, Citra, Columbus</t>
-  </si>
-  <si>
-    <t>Пиво Saldens American IPA Six Hops 0,45</t>
-  </si>
-  <si>
-    <t>Х1728</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/6068ac02-91c3-4398-8fd0-97fd7325545a
- https://online.sbis.ru/fs-public/ekt_files/8f2d18b0-891c-412b-858c-b619c6d244f7</t>
-  </si>
-  <si>
-    <t>7% ABV IPA - American 60 IBU
-На сухом охмелении: Amarillo, Columbus, Simcoe, Citra, Mosaic, Centennial</t>
-  </si>
-  <si>
-    <t>Пиво Saldens Cold Double IPA 0.45</t>
-  </si>
-  <si>
-    <t>Х2267</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/290ed07f-37a4-431d-b24e-306f33424acb
- https://online.sbis.ru/fs-public/ekt_files/86f7fe7b-26f3-4b9a-9691-cf2db97cbcbd</t>
-  </si>
-  <si>
-    <t>8.5% ABV IPA - Cold 100 IBU</t>
-  </si>
-  <si>
-    <t>Пиво Saldens Hazelnut Stout 0.45</t>
-  </si>
-  <si>
-    <t>Х2266</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/6e3a4c90-1d0e-423d-8bcf-6922bf5f05b3
- https://online.sbis.ru/fs-public/ekt_files/804cd600-d55b-4a9b-98a8-b4199c7acd59</t>
-  </si>
-  <si>
-    <t>7% ABV Stout - Pastry
-Brewed with Lactose</t>
-  </si>
-  <si>
-    <t>Пиво Saldens Lime IPA</t>
-  </si>
-  <si>
-    <t>Х1882</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d9058dc6-4892-48c9-a884-9f8f00d71bef
- https://online.sbis.ru/fs-public/ekt_files/0533865e-b7af-414a-9ff3-c6298c931570</t>
-  </si>
-  <si>
-    <t>7% ABV IPA - Fruited 60 IBU
-Сухое охмеление хмелями Cascade, Chinook.
-С добавлением сока лайма</t>
   </si>
   <si>
     <t>Пиво Saldens Michelada Ed</t>
@@ -727,6 +478,47 @@
   </si>
   <si>
     <t>Классический мид с добавлением сока спелой вишни. Летний легкий вкус без кислотности.</t>
+  </si>
+  <si>
+    <t>Медовуха Steppe &amp; Wind Мед и Грейпфрут</t>
+  </si>
+  <si>
+    <t>Х598</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/9fdb69c4-1bc7-4154-a573-9713e92cf2ad</t>
+  </si>
+  <si>
+    <t>6% ABV N/A IBU Mead - Melomel
+Липовый мёд и горы грейпфрута. Всё, чтобы соответствовать топовым в России сортам;)</t>
+  </si>
+  <si>
+    <t>Медовуха Степь и Ветер Black Currant &amp; Lime</t>
+  </si>
+  <si>
+    <t>Х2281</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/0ec5104a-546b-4674-905c-f3886d511a10
+ https://online.sbis.ru/fs-public/ekt_files/266ab118-0752-4c1f-9470-322cf3794dd1</t>
+  </si>
+  <si>
+    <t>6% ABV Mead - Melomel
+Сложный, сбалансированный вкус, в котором яркая кислинка чёрной смородины и свежесть лайма сочетаются с тёплой пряностью кардамона.</t>
+  </si>
+  <si>
+    <t>Медовуха Степь и Ветер Blueberry Mead(Черника)</t>
+  </si>
+  <si>
+    <t>Х2186</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/be223a0a-09a4-461b-bbe0-44bde6d4756c
+ https://online.sbis.ru/fs-public/ekt_files/20b1f8b4-6487-491e-aa53-1b7bb871063c</t>
+  </si>
+  <si>
+    <t>4.5% ABV Mead - Melomel
+Новый взгляд на классику: в основе наш традиционный мёд, к которому мы добавили сок спелой черники. Сбалансированно, свежо, без излишней сладости.</t>
   </si>
   <si>
     <t>Медовуха Степь и Ветер Cola Mead 0.33</t>
@@ -759,45 +551,17 @@
 В составе сброженный карамелизированный мёд с малиной и черникой.</t>
   </si>
   <si>
-    <t>Медовуха Степь и Ветер Smoothie Mead: Raspberry, Black Currant, Mint</t>
-  </si>
-  <si>
-    <t>Х1445</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/8ea1a8bf-91ed-4dba-b206-77660c1b76b9
- https://online.sbis.ru/fs-public/ekt_files/ed2882c9-c8fd-4d71-b7e0-0ee08a018cf3</t>
-  </si>
-  <si>
-    <t>6% ABV N/A IBU Mead - Other
-Смузи мёд с малиной, чёрной смородиной и мятой. Менее плотный напиток из-за более нежной структуры ягодных пюре. Малина добавляет сладости, смородина интересную терпкость с кислинкой, а на послевкусии освежающая мята. Насыщенный ягодный смузи.</t>
-  </si>
-  <si>
-    <t>Медовуха Степь и Ветер Ананас Лайм</t>
-  </si>
-  <si>
-    <t>Х2256</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/5f3103b4-a524-4a51-8611-ab5d5abbf317
- https://online.sbis.ru/fs-public/ekt_files/d67eeb28-5534-435e-be87-ec78a5af69f2</t>
-  </si>
-  <si>
-    <t>Mead - Melomel 4.5% ABV
-Ананас, лайм и немного мяты для свежести. Хотелось экзотики, но лёгкой и похожей на фруктовый берлинер вайс, но в мире мёда. Использовали соки прямого отжима, чтобы сохранить всю сочность и свежесть ананаса и лайма.</t>
-  </si>
-  <si>
-    <t>Медовуха Степь и Ветер Мёд, ваниль и Черника</t>
-  </si>
-  <si>
-    <t>Х1640</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/36fa332b-c1eb-4a11-9dd3-18ac3e8d698b</t>
-  </si>
-  <si>
-    <t>6% ABV Mead - Session N/A IBU
-Мёд, черничной сок и ваниль. В меру сладко и терпко, с приятным ароматом ванили.</t>
+    <t>Медовуха Степь и Ветер Малина(Raspberry Mead)</t>
+  </si>
+  <si>
+    <t>Х2279</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/a8c9568a-86b7-41ce-a50b-ecfd49dba0fd</t>
+  </si>
+  <si>
+    <t>4.5% ABV Mead - Melomel
+Здесь всё крутится вокруг малины: сочная, ароматная, с той самой лёгкой кислинкой, которая идеально подружилась с нашим традиционным мидом.</t>
   </si>
   <si>
     <t>Медовуха Степь и Ветер Мед и Абрикос(Apricot)</t>
@@ -839,6 +603,21 @@
 Мы взяли наш традиционный мёд, тот самый, который все любят, сохранили его глубину и натуральную сладость, но добавили новый акцент — сок спелой клубники. Получился тот самый любимый мёд, но с приятной ягодной ноткой. Просто, вкусно и без лишних сложностей.</t>
   </si>
   <si>
+    <t>Медовуха Степь и Ветер Мёд и Мята</t>
+  </si>
+  <si>
+    <t>Х2280</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/df066424-c8ef-4ec2-bbf4-f57687362bf9
+ https://online.sbis.ru/fs-public/ekt_files/01a0623c-cc2c-74b2-b73e-472b031e91d1</t>
+  </si>
+  <si>
+    <t>4.5% ABV Mead - Traditional
+Идеальный рецепт: хорошо сброженный мёд и щедрая порция свежезаваренной мяты.
+Свежий, легкий и летний вкус. Такой традишнл, который остался самим собой, но обзавёлся приятным мятным холодком.</t>
+  </si>
+  <si>
     <t>Медовуха Степь и Ветер Мёд и Смородина(Black Currant)</t>
   </si>
   <si>
@@ -866,6 +645,23 @@
 Это базовый мид из цветочного мёда сброженный с дубовой щепой. Медовуха, как она есть. Наше видение баланса в угоду питкости и умеренной цены.</t>
   </si>
   <si>
+    <t>Медовуха Степь и Ветер Шарлотка</t>
+  </si>
+  <si>
+    <t>Х2282</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/09c4a98d-bef2-41ed-96e8-b95d5e57b18c
+ https://online.sbis.ru/fs-public/ekt_files/52a28203-3787-4d63-bb0d-404ccc0ef62d</t>
+  </si>
+  <si>
+    <t>6% ABV Mead - Other
+Же мапель Шарлотка!
+Лё калабарасьон авек Ля Теори Дю Гранд Пиво!
+Лё яблочний мерд авэк бисквит Юбилейное!
+Бон апети, ле комрад!</t>
+  </si>
+  <si>
     <t>Василеостровская пивоварная</t>
   </si>
   <si>
@@ -937,6 +733,20 @@
   <si>
     <t>ABV 4.0% Lager
 Светлое пиво насыщенного янтарного цвета с приятными хмелевыми нотками и характерным вкусом карамельного солода</t>
+  </si>
+  <si>
+    <t>Пиво Чепецкое Темное</t>
+  </si>
+  <si>
+    <t>Х1699</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/eebcde88-6f5a-466b-a41a-a0d8b86f5ce9
+ https://online.sbis.ru/fs-public/ekt_files/a2bf74b0-a4ed-4e11-8385-a3126ae70fa5</t>
+  </si>
+  <si>
+    <t>ABV 4.1% Lager Dark
+Мюнхенский и карамельный солод придают пиву насыщенный красновато–коричневый цвет и мягкий карамельный вкус с длительным солодовым послевкусием.</t>
   </si>
   <si>
     <t>Пиво безалко</t>
@@ -967,6 +777,46 @@
   <si>
     <t>ABV 0,5%
 Светлое пиво с превосходным вкусом, который обеспечивают ингредиенты наивысшего качества. Для сохранения классического вкуса пива используется уникальная технология производства с добавлением в рецептуру импортного чешского хмеля.</t>
+  </si>
+  <si>
+    <t>Пиво Горьковская IPA б/а 0,33#</t>
+  </si>
+  <si>
+    <t>X3132592</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d2885835-5408-4a72-a4a4-bbf5102c939a</t>
+  </si>
+  <si>
+    <t>ABV 0.0% IPA
+Обладает ярко выраженным ароматом цитрусовых (грейпфрут, лайм) и нотами тропических фруктов с комфортной хмелевой горечью. Пиво хорошо освежает и обладает легким послевкусием.</t>
+  </si>
+  <si>
+    <t>Пиво Black Cat 80 ДИПА</t>
+  </si>
+  <si>
+    <t>Х2277</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/a2e66fae-3b06-42b1-83e5-52a7d9c8e212
+ https://online.sbis.ru/fs-public/ekt_files/1a0f38cc-3243-4ad8-8018-58a0c557ee6a</t>
+  </si>
+  <si>
+    <t>8.2% ABV IPA - Imperial / Double 80 IBU
+Продолжение поиска новых форм в сухих IPA, сваренных в американском стиле. Более плотное тело пива по сравнению с «младшим братом» - 70 IPAтакже не содержит карамельных солодов, оно шелковистое благодаря добавлению овсяных хлопьев, а щедрое многоступенчатое охмеление Simcoe &amp; Mosaic придает пиву уверенную округлую горечь, и цитрусовый аромат.</t>
+  </si>
+  <si>
+    <t>Пиво Black Cat Облачка</t>
+  </si>
+  <si>
+    <t>Х2276</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/2f33adf2-7dab-42a2-b740-e2f6867ac02d</t>
+  </si>
+  <si>
+    <t>6% ABV 20 IBU IPA - New England / Hazy
+NE IPA охмеленная Idaho 7 Cryo, Citra lupomax и Galaxy</t>
   </si>
   <si>
     <t>Пиво ВАСЬКА ПШЕНИЧНОЕ</t>
@@ -1379,7 +1229,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="93.42578125" customWidth="1"/>
@@ -1445,7 +1295,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="4">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -1462,7 +1312,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="4">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
@@ -1479,7 +1329,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="4">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>19</v>
@@ -1496,7 +1346,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="4">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>23</v>
@@ -1513,7 +1363,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="4">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>27</v>
@@ -1530,7 +1380,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="4">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>31</v>
@@ -1547,12 +1397,12 @@
         <v>34</v>
       </c>
       <c r="B10" s="4">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -1564,7 +1414,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="4">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>39</v>
@@ -1581,7 +1431,7 @@
         <v>42</v>
       </c>
       <c r="B12" s="4">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>43</v>
@@ -1593,94 +1443,94 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:5" outlineLevel="2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:5" outlineLevel="1">
+      <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="4">
-        <v>380</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>49</v>
+      <c r="E13" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" outlineLevel="2">
       <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4">
+        <v>370</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="4">
-        <v>420</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:5" outlineLevel="1">
+      <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" outlineLevel="2">
-      <c r="A15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B15" s="4">
-        <v>420</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5" outlineLevel="2">
       <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4">
+        <v>400</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B16" s="4">
-        <v>390</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5" outlineLevel="2">
       <c r="A17" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" s="4">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:5" outlineLevel="1">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>6</v>
@@ -1689,355 +1539,355 @@
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:5" outlineLevel="2">
       <c r="A19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4">
+        <v>349</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" outlineLevel="1">
+      <c r="A20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="4">
-        <v>420</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" outlineLevel="2">
+      <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="B21" s="4">
+        <v>325</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" outlineLevel="2">
-      <c r="A20" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="4">
-        <v>370</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" outlineLevel="1">
-      <c r="A21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:5" outlineLevel="2">
       <c r="A22" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:5" outlineLevel="2">
       <c r="A23" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B23" s="4">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:5" outlineLevel="2">
       <c r="A24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="4">
+        <v>370</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" outlineLevel="1">
+      <c r="A25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="4">
-        <v>415</v>
-      </c>
-      <c r="C24" s="3" t="s">
+    </row>
+    <row r="26" spans="1:5" outlineLevel="2">
+      <c r="A26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="B26" s="4">
+        <v>370</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="D26" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" outlineLevel="2">
-      <c r="A25" s="3" t="s">
+      <c r="E26" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B25" s="4">
-        <v>415</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" outlineLevel="1">
-      <c r="A26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:5" outlineLevel="2">
       <c r="A27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="4">
+        <v>370</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" outlineLevel="1">
+      <c r="A28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B27" s="4">
-        <v>299</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="B28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" outlineLevel="2">
-      <c r="A28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="4">
-        <v>289</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:5" outlineLevel="2">
       <c r="A29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="4">
+        <v>360</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" outlineLevel="1">
+      <c r="A30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B29" s="4">
-        <v>299</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="E30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" outlineLevel="2">
+      <c r="A31" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="B31" s="4">
+        <v>360</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="D31" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" outlineLevel="2">
-      <c r="A30" s="3" t="s">
+      <c r="E31" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="4">
-        <v>269</v>
-      </c>
-      <c r="C30" s="3" t="s">
+    </row>
+    <row r="32" spans="1:5" outlineLevel="1">
+      <c r="A32" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="B32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" outlineLevel="1">
-      <c r="A31" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" outlineLevel="2">
-      <c r="A32" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="4">
-        <v>325</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>117</v>
+      <c r="E32" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" outlineLevel="2">
       <c r="A33" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B33" s="4">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:5" outlineLevel="2">
       <c r="A34" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B34" s="4">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:5" outlineLevel="2">
       <c r="A35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="4">
+        <v>360</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" outlineLevel="2">
+      <c r="A36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="4">
+        <v>360</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="4">
-        <v>370</v>
-      </c>
-      <c r="C35" s="3" t="s">
+    </row>
+    <row r="37" spans="1:5" outlineLevel="1">
+      <c r="A37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="B37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" outlineLevel="1">
-      <c r="A36" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" outlineLevel="2">
-      <c r="A37" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="4">
-        <v>370</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>135</v>
+      <c r="E37" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:5" outlineLevel="2">
       <c r="A38" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B38" s="4">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:5" outlineLevel="1">
       <c r="A39" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>6</v>
@@ -2046,740 +1896,553 @@
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:5" outlineLevel="2">
       <c r="A40" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B40" s="4">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:5" outlineLevel="2">
       <c r="A41" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B41" s="4">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>149</v>
+        <v>140</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" outlineLevel="1">
-      <c r="A42" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>6</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" outlineLevel="2">
+      <c r="A42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="4">
+        <v>380</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:5" outlineLevel="2">
       <c r="A43" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B43" s="4">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:5" outlineLevel="2">
       <c r="A44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="4">
+        <v>332</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" outlineLevel="2">
+      <c r="A45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="4">
+        <v>385</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B44" s="4">
-        <v>380</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="E45" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" outlineLevel="1">
-      <c r="A45" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5" outlineLevel="2">
       <c r="A46" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B46" s="4">
-        <v>350</v>
+        <v>265</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:5" outlineLevel="2">
       <c r="A47" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B47" s="4">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:5" outlineLevel="2">
       <c r="A48" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B48" s="4">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:5" outlineLevel="2">
       <c r="A49" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B49" s="4">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:5" outlineLevel="2">
       <c r="A50" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B50" s="4">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:5" outlineLevel="2">
       <c r="A51" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B51" s="4">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:5" outlineLevel="2">
       <c r="A52" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B52" s="4">
-        <v>360</v>
+        <v>245</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:5" outlineLevel="2">
       <c r="A53" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="4">
+        <v>390</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" outlineLevel="1">
+      <c r="A54" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B53" s="4">
-        <v>360</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="B54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" outlineLevel="2">
+      <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="B55" s="4">
+        <v>449</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" outlineLevel="2">
-      <c r="A54" s="3" t="s">
+      <c r="D55" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="4">
-        <v>360</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="E55" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="D54" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5" outlineLevel="1">
+      <c r="A56" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="B56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" outlineLevel="2">
+      <c r="A57" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" outlineLevel="1">
-      <c r="A55" s="1" t="s">
+      <c r="B57" s="4">
+        <v>229</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" outlineLevel="2">
-      <c r="A56" s="3" t="s">
+      <c r="E57" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="B56" s="4">
-        <v>365</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" outlineLevel="1">
-      <c r="A57" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:5" outlineLevel="2">
       <c r="A58" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B58" s="4">
-        <v>345</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:5" outlineLevel="2">
       <c r="A59" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B59" s="4">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:5" outlineLevel="2">
       <c r="A60" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B60" s="4">
-        <v>385</v>
+        <v>199</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" outlineLevel="2">
       <c r="A61" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B61" s="4">
-        <v>400</v>
+        <v>199</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" outlineLevel="2">
-      <c r="A62" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B62" s="4">
-        <v>373</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>226</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" outlineLevel="1">
+      <c r="A62" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:5" outlineLevel="2">
       <c r="A63" s="3" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B63" s="4">
-        <v>385</v>
+        <v>165</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>230</v>
+        <v>220</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:5" outlineLevel="2">
       <c r="A64" s="3" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B64" s="4">
-        <v>345</v>
+        <v>229</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:5" outlineLevel="2">
       <c r="A65" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B65" s="4">
+        <v>170</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" outlineLevel="1">
+      <c r="A66" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B66" s="4">
+        <v>370</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" outlineLevel="1">
+      <c r="A67" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B67" s="4">
+        <v>390</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B65" s="4">
-        <v>345</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="E67" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E65" s="5" t="s">
+    </row>
+    <row r="68" spans="1:5" outlineLevel="1">
+      <c r="A68" s="3" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" outlineLevel="2">
-      <c r="A66" s="3" t="s">
+      <c r="B68" s="4">
         <v>239</v>
       </c>
-      <c r="B66" s="4">
-        <v>265</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="C68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="E68" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" outlineLevel="1">
+      <c r="A69" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="B69" s="4">
+        <v>239</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" outlineLevel="2">
-      <c r="A67" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B67" s="4">
-        <v>345</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="E69" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" outlineLevel="1">
+      <c r="A70" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="B70" s="4">
+        <v>239</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="D70" s="3" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" outlineLevel="2">
-      <c r="A68" s="3" t="s">
+      <c r="E70" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" outlineLevel="1">
+      <c r="A71" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B68" s="4">
-        <v>245</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="B71" s="4">
+        <v>219</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D71" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" outlineLevel="1">
-      <c r="A69" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" outlineLevel="2">
-      <c r="A70" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B70" s="4">
-        <v>449</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" outlineLevel="1">
-      <c r="A71" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" outlineLevel="2">
-      <c r="A72" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B72" s="4">
-        <v>229</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" outlineLevel="2">
-      <c r="A73" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B73" s="4">
-        <v>249</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" outlineLevel="2">
-      <c r="A74" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B74" s="4">
-        <v>249</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" outlineLevel="2">
-      <c r="A75" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B75" s="4">
-        <v>199</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" outlineLevel="1">
-      <c r="A76" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" outlineLevel="2">
-      <c r="A77" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B77" s="4">
-        <v>165</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" outlineLevel="2">
-      <c r="A78" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B78" s="4">
-        <v>229</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" outlineLevel="1">
-      <c r="A79" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B79" s="4">
-        <v>239</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" outlineLevel="1">
-      <c r="A80" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B80" s="4">
-        <v>239</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" outlineLevel="1">
-      <c r="A81" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B81" s="4">
-        <v>239</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" outlineLevel="1">
-      <c r="A82" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B82" s="4">
-        <v>219</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E82" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>6</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="287">
   <si>
     <t>Наименование</t>
   </si>
@@ -133,18 +133,18 @@
 Насыщенный кислый и прозрачный эль. Сочная томатная база, немного соли и выраженные ноты кориандра, лаврового листа, базилика, паприки и чеснока.</t>
   </si>
   <si>
-    <t>Пиво BAD Груша Блю Чиз</t>
-  </si>
-  <si>
-    <t>Х2250</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/32c60627-8d68-4e03-be7f-4302f3d59f37</t>
-  </si>
-  <si>
-    <t>5.5% ABV Sour - Smoothie / Pastry
-Сладость спелой груши — нежная, как первый поцелуй, оставляющий томное влажное послевкусие желания. Кислинка пробегает искрой по позвоночнику, заставляя нежно выгнуть спину от удовольствия.
-А потом... глубокий шепот голубого сыра. Пикантный, дерзкий, солоноватый оттенок проникает глубоко, нарушая правила. Игра контрастов: сладость и соль, нежность, подчинение и власть.</t>
+    <t>Пиво 4Brewers Манго+Клубника</t>
+  </si>
+  <si>
+    <t>Х2288</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/04077f16-816e-48a5-8f1a-0f323873a80a
+ https://online.sbis.ru/fs-public/ekt_files/d70f254d-62e9-40bb-8b3a-04bb90ebaf8d</t>
+  </si>
+  <si>
+    <t>6% ABV Sour - Smoothie / Pastry
+Густой насыщенный кислый эль. Яркий аромат и вкус клубники и манго, умеренная кислотность и консистенция смузи.</t>
   </si>
   <si>
     <t>Пиво BAD ПЕЧЕНЬЕ С АПЕЛЬСИНОМ И ШОКОЛАДОМ</t>
@@ -181,6 +181,48 @@
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d7ede847-6816-4fec-876d-5d8590960aa5</t>
   </si>
   <si>
+    <t>Пиво BAD CHOCOLATE PASTE</t>
+  </si>
+  <si>
+    <t>Х2108</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/29db16dc-f6e2-4834-8442-21d65c8e0523
+ https://online.sbis.ru/fs-public/ekt_files/0f1b31db-4629-4c9e-85e8-1517358fba03</t>
+  </si>
+  <si>
+    <t>7% ABV Stout - Imperial / Double
+Дабл стаут с шоколадной пастой - это воспоминание в бокале о полуночном походе к холодильнику, где ты, затаив дыхание, вычерпывал последние густые следы пасты прямо из банки.</t>
+  </si>
+  <si>
+    <t>Пиво BAD ECLAIR WITH COCONUT AND LICHIE</t>
+  </si>
+  <si>
+    <t>Х2292</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/9cdf7112-ee0e-48f4-ba79-c688a72a2090
+ https://online.sbis.ru/fs-public/ekt_files/14194f01-ac64-4ad1-860f-b1c79ae7cf1a</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Smoothie / Pastry
+Нежный, как объятия после свидания, наш смузи саур эль эклер с тропическими оттенками - это настоящая игра для твоих вкусовых рецепторов.</t>
+  </si>
+  <si>
+    <t>Пиво BAD OATMEAL COOKIE WITH PINE NUTS</t>
+  </si>
+  <si>
+    <t>Х2291</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/28a55d2b-3012-4906-b845-327af3e9c70f
+ https://online.sbis.ru/fs-public/ekt_files/7ecd009e-e2bd-4341-a41a-d0d05aa930ce</t>
+  </si>
+  <si>
+    <t>7% ABV Stout - Imperial / Double
+Наш стаут - как тёмное признание в бокале: гуще, глубже, насыщеннее. Его аромат - обволакивающий шёпот свежеиспечённого овсяного печенья, тёплая ваниль, карамель с лёгким дымком и томная, маслянистая глубина кедрового ореха, раскрывающаяся с благородной пряностью.</t>
+  </si>
+  <si>
     <t>Пиво BAD WAFFLE WITH MELON  AND BANANA</t>
   </si>
   <si>
@@ -220,6 +262,65 @@
   </si>
   <si>
     <t>Х2258</t>
+  </si>
+  <si>
+    <t>Brewman</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/ec873f2c-a29c-4433-aa5f-547f43b76e09</t>
+  </si>
+  <si>
+    <t>Мы ищем лучшие рецепты – подлинные сокровища пивоваренной культуры Мира. Если Вы хотите найти наиболее подходящий для Вас вкус, начните свое путешествие с Brewmen.</t>
+  </si>
+  <si>
+    <t>Пиво Brewmen Maybe Milk?</t>
+  </si>
+  <si>
+    <t>Х2054</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d49ac66e-2b9f-4e87-be07-7098ca2c16d1</t>
+  </si>
+  <si>
+    <t>6.5% ABV Stout - Milk / Sweet 10 IBU
+Плотный, насыщенный чёрный сладкий стаут с ароматом бисквита и вкусом шоколада.
+C добавлением лактозы и не сбраживаемых сахаров для сладости и оно становится густым и питким и мягким.
+Аромат: шоколадно-бисквитный, отдалённо напоминает запах капучино
+с шоколадным сиропом.</t>
+  </si>
+  <si>
+    <t>Burning Brewery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/0add27fa-9ea0-4017-b033-731ce0db71a1</t>
+  </si>
+  <si>
+    <t>Пиво Burning Brewery Копченая скумбрия</t>
+  </si>
+  <si>
+    <t>Х2289</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/de9b916e-badd-47e8-8d83-42810642f04e
+ https://online.sbis.ru/fs-public/ekt_files/01a1106e-fb5f-7936-82d6-5ea7f20a2ae2</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Other Gose
+Вы точно готовы открыть эту банку? Потому что внутри — тот самый копчёный вкус, который обычно лежит на газетке к пиву.</t>
+  </si>
+  <si>
+    <t>Пиво Burning Brewery Сырный Чили Соус</t>
+  </si>
+  <si>
+    <t>Х2290</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/795a615d-5d09-4a6a-8838-7f319e47f082
+ https://online.sbis.ru/fs-public/ekt_files/019f8de1-2829-75a5-a95c-2955d725ddb6</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Other Gose
+Гозе «Сырный Чили» — ваша любимая закуска в формате соуса, теперь в бокале. Этот напиток воссоздаёт тот самый вкус маленького контейнера с сырным соусом, который идеален для чипсов и начос.</t>
   </si>
   <si>
     <t>Hangar</t>
@@ -234,6 +335,32 @@
 авиаклуб ОСОАВИАХИМа.</t>
   </si>
   <si>
+    <t>Пиво Hangar Винговер</t>
+  </si>
+  <si>
+    <t>Х2072</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/b71ffac8-8047-43a2-8286-545b9a551ee7</t>
+  </si>
+  <si>
+    <t>ABV 4.5% Pale Ale
+Классический английский эль с насыщенной палитрой, где солодовые ноты светлого и карамельного ячменя взмывают вверх, совершая маневр высшего пилотажа в чистом небе.</t>
+  </si>
+  <si>
+    <t>Пиво Hangar Жар-Птица</t>
+  </si>
+  <si>
+    <t>Х2073</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d0271ac3-00da-4afd-976f-77608485eae1</t>
+  </si>
+  <si>
+    <t>ABV 5.0% Amber Ale
+Насыщенный и теплый, с бархатистой солодовой сладостью и яркими карамельными отблесками, словно закатное солнце на крыльях знаменитого биплана.</t>
+  </si>
+  <si>
     <t>Пиво Hangar Полет Шмеля</t>
   </si>
   <si>
@@ -247,24 +374,23 @@
 Плотный и насыщенный, он сочетает в себе мягкие солодовые оттенки светлого и карамельного ячменя с тонкой, но выразительной хмелевой горчинкой – как точные приборы и мощные двигатели, обеспечивающие стабильность полета.</t>
   </si>
   <si>
+    <t>Пиво Hangar Полярный Бланш</t>
+  </si>
+  <si>
+    <t>Х2078</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/07bf9c4c-3ca2-4c32-812f-f5cda2fa1548</t>
+  </si>
+  <si>
+    <t>ABV 4.6 Blanche/Belgian White
+Мягкий и пряный, с цитрусовой свежестью апельсиновой цедры и кориандровыми нотками, словно холодный ветер в кабине легендарного АН-2. Пшеничный, ячменный и овсяный солоды дарят бархатистую текстуру и легкую сладость, а хмель добавляет горчинку</t>
+  </si>
+  <si>
     <t>Jaws</t>
   </si>
   <si>
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/0c86492e-34af-44fa-af00-ecd9ff0add64</t>
-  </si>
-  <si>
-    <t>Пиво Jaws Nitro Stout</t>
-  </si>
-  <si>
-    <t>Х802</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/6f676b0a-6137-4fc0-b1ff-e9e7271dec8a
- https://online.sbis.ru/fs-public/ekt_files/4bdeb3dc-7c12-44fd-bd28-f3b7de537ede</t>
-  </si>
-  <si>
-    <t>6% ABV 20 IBU Stout - Milk / Sweet
-Тающая сливочная пена, плотный вкус шоколадного пудинга и магия лавинного эффекта азотных пузырьков, – наш взгляд на нитро стаут новой волны. 7 солодов и 6 процентов крепости уводят вкус любимого стиля в убедительный отрыв!</t>
   </si>
   <si>
     <t>Пиво Jaws Red Widow 0.5</t>
@@ -278,18 +404,6 @@
   <si>
     <t>8% ABV Belgian Strong Dark Ale 35 IBU
 Упоительная коварность вишнёвого вкуса! Сочность зрелых ягод, сбалансированная винность и деликатные оттенки косточки в послевкусии, - главные слагаемые нашей "Вишнёвой вдовы". Будьте с ней осторожны!</t>
-  </si>
-  <si>
-    <t>Пиво Jaws Атомная прачечная ИПА</t>
-  </si>
-  <si>
-    <t>Х799</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://online.sbis.ru/fs-public/ekt_files/55e3f513-e6a9-47f3-90e9-ad8e375e5565</t>
-  </si>
-  <si>
-    <t>Тёмный насыщенный эль. Сладкий, плотный, согревающий. Выраженный вкус и аромат вяленых бананов балансируется кофейностью и шоколадностью тёмных солодов.</t>
   </si>
   <si>
     <t>Пиво Jaws «Джазз энд Джус»</t>
@@ -362,6 +476,34 @@
 "Пробили стаут вместо саура? Гааааля, у нас отмеееееена! Учини скандал и требуй администратора, ведь не только ты хочешь #buy_it. Сочный манговый саур, плотный, как очередь на кассу, с кислинкой грейпфрута и свежим ананасовым послевкусием просто обязан упасть в твою пивную корзинку.</t>
   </si>
   <si>
+    <t>Пиво Magic Mess Оракул</t>
+  </si>
+  <si>
+    <t>Х2287</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/340d0814-e5cb-47b9-8031-a6ba626bbdc8
+ https://online.sbis.ru/fs-public/ekt_files/da97811a-744f-467f-a3f7-97f63b72a450</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Fruited
+Если судьба подсказывает взять дыню с кислой смородиной, спорить с ней не стоит! Глубокий, кисло-сладкий вкус — для избранных, кто точно знает, чего хочет от жизни.</t>
+  </si>
+  <si>
+    <t>Пиво Magic Mess Транжира</t>
+  </si>
+  <si>
+    <t>Х2286</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/03a210f5-4d00-4f5d-9571-036f665ed8c3
+ https://online.sbis.ru/fs-public/ekt_files/8c26d9af-34fe-43e8-950b-f7455c8d78c2</t>
+  </si>
+  <si>
+    <t>5.5% ABV Sour - Fruited
+Арбуз, дыня, зелёное яблоко — фруктовый взрыв для тех, кто знает: чем больше тратишь на себя, тем больше тебе возвращается! Пора попробовать на вкус финансовую грамотность.</t>
+  </si>
+  <si>
     <t>Panzer Brewery</t>
   </si>
   <si>
@@ -387,6 +529,20 @@
     <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/d4e7177f-3ee7-40b4-9481-8bad8d920f59</t>
   </si>
   <si>
+    <t>Пиво Saldens American IPA Six Hops 0,45</t>
+  </si>
+  <si>
+    <t>Х1728</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/6068ac02-91c3-4398-8fd0-97fd7325545a
+ https://online.sbis.ru/fs-public/ekt_files/8f2d18b0-891c-412b-858c-b619c6d244f7</t>
+  </si>
+  <si>
+    <t>7% ABV IPA - American 60 IBU
+На сухом охмелении: Amarillo, Columbus, Simcoe, Citra, Mosaic, Centennial</t>
+  </si>
+  <si>
     <t>Пиво Saldens Michelada Ed</t>
   </si>
   <si>
@@ -414,20 +570,6 @@
 Двойной IPA в стиле западного побережья США на охмелении которого использовались по-настоящему олдскульные хмели Goldings, Cascade, Columbus и Chinook, радующие всех любителей охмелённого пива уже не один десяток лет, что и отражено в названии сорта.</t>
   </si>
   <si>
-    <t>Пиво Saldens Sultana IPA</t>
-  </si>
-  <si>
-    <t>Х2265</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/bb0c43aa-b670-4862-a8e9-b234041eba4c
- https://online.sbis.ru/fs-public/ekt_files/1a486724-fc66-4719-8ed7-8b44de341a75</t>
-  </si>
-  <si>
-    <t>7% ABV IPA - American 60 IBU
-Hops: Sultana</t>
-  </si>
-  <si>
     <t>Пиво Saldens Tomato Gose Extra Hot Ed</t>
   </si>
   <si>
@@ -519,20 +661,6 @@
   <si>
     <t>4.5% ABV Mead - Melomel
 Новый взгляд на классику: в основе наш традиционный мёд, к которому мы добавили сок спелой черники. Сбалансированно, свежо, без излишней сладости.</t>
-  </si>
-  <si>
-    <t>Медовуха Степь и Ветер Cola Mead 0.33</t>
-  </si>
-  <si>
-    <t>Х2132</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/55cc42de-ef32-4555-bd41-4f22ad10fa30
- https://online.sbis.ru/fs-public/ekt_files/56dbf92f-2fdb-462b-8199-25fea1741470</t>
-  </si>
-  <si>
-    <t>6% ABV Mead - Bochet
-Мёд с карамельной сладостью и щедрым кардамоном. Корица, ваниль и гвоздика складываются в знакомый вкус колы, но теплее и богаче. Кориандр добавляет цитрусовую искру. Получился медовый вариант легендарного напитка — пряный, сладкий и освежающий.</t>
   </si>
   <si>
     <t>Медовуха Степь и Ветер Raspberry &amp; Blueberry Bochet</t>
@@ -588,19 +716,6 @@
   <si>
     <t>6% ABV N/A IBU Mead - Session / Short
 Медовуха с добавлением ежевики</t>
-  </si>
-  <si>
-    <t>Медовуха Степь и Ветер Мед и Клубника(Strawberry)</t>
-  </si>
-  <si>
-    <t>Х2130</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/db8e802d-cad3-4019-8613-4d83aa3cc67a</t>
-  </si>
-  <si>
-    <t>4.5% ABV Mead - Melomel
-Мы взяли наш традиционный мёд, тот самый, который все любят, сохранили его глубину и натуральную сладость, но добавили новый акцент — сок спелой клубники. Получился тот самый любимый мёд, но с приятной ягодной ноткой. Просто, вкусно и без лишних сложностей.</t>
   </si>
   <si>
     <t>Медовуха Степь и Ветер Мёд и Мята</t>
@@ -696,6 +811,20 @@
   <si>
     <t>ABV 4.9% 15 IBU Wheat Beer - Witbier / Blanche
 Эталон сорта бланш, бельгийского нефильтрованного пшеничного пива. Обладает многогранным уникальным вкусом: мягкое, легкое, с нотками пряностей и цитрусовых и едва различимой хмелевой горчинкой</t>
+  </si>
+  <si>
+    <t>Пиво Spaten Hell германия</t>
+  </si>
+  <si>
+    <t>Х2261</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://disk.saby.ru/disk/api/v1/a81849e7-16fd-4d3d-90cb-143ce4e05f32
+ https://online.sbis.ru/fs-public/ekt_files/6c06beac-e05a-4ee1-8f55-631eb35b456d</t>
+  </si>
+  <si>
+    <t>5.2% ABV Lager - Helles 21 IBU
+Оригинальный Шпатен из Германии</t>
   </si>
   <si>
     <t>Пиво Stella Artois</t>
@@ -1229,7 +1358,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="93.42578125" customWidth="1"/>
@@ -1397,12 +1526,12 @@
         <v>34</v>
       </c>
       <c r="B10" s="4">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -1470,67 +1599,67 @@
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:5" outlineLevel="1">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:5" outlineLevel="2">
+      <c r="A15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="4">
+        <v>420</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>54</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:5" outlineLevel="2">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="4">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="D16" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:5" outlineLevel="2">
       <c r="A17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="4">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:5" outlineLevel="1">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>6</v>
@@ -1539,95 +1668,95 @@
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:5" outlineLevel="2">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" outlineLevel="1">
-      <c r="A20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" outlineLevel="2">
-      <c r="A21" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="4">
-        <v>325</v>
-      </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="20" spans="1:5" outlineLevel="2">
+      <c r="A20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="B20" s="4">
+        <v>415</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" outlineLevel="1">
+      <c r="A21" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" outlineLevel="2">
       <c r="A22" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B22" s="4">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" outlineLevel="2">
-      <c r="A23" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="4">
-        <v>370</v>
-      </c>
-      <c r="C23" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="3" t="s">
+    </row>
+    <row r="23" spans="1:5" outlineLevel="1">
+      <c r="A23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>81</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:5" outlineLevel="2">
@@ -1635,225 +1764,225 @@
         <v>82</v>
       </c>
       <c r="B24" s="4">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" outlineLevel="1">
-      <c r="A25" s="1" t="s">
+      <c r="E24" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="1" t="s">
+    </row>
+    <row r="25" spans="1:5" outlineLevel="2">
+      <c r="A25" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="B25" s="4">
+        <v>400</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" outlineLevel="2">
-      <c r="A26" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="4">
-        <v>370</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="E25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="3" t="s">
+    </row>
+    <row r="26" spans="1:5" outlineLevel="1">
+      <c r="A26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="B26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>91</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:5" outlineLevel="2">
       <c r="A27" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="4">
-        <v>370</v>
+        <v>299</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="5" t="s">
         <v>94</v>
       </c>
+      <c r="D27" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="E27" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" outlineLevel="1">
-      <c r="A28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="1" t="s">
+    </row>
+    <row r="28" spans="1:5" outlineLevel="2">
+      <c r="A28" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="B28" s="4">
+        <v>289</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>98</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:5" outlineLevel="2">
       <c r="A29" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B29" s="4">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" outlineLevel="1">
-      <c r="A30" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" outlineLevel="2">
-      <c r="A31" s="3" t="s">
+    </row>
+    <row r="30" spans="1:5" outlineLevel="2">
+      <c r="A30" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="4">
-        <v>360</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B30" s="4">
+        <v>320</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:5" outlineLevel="1">
-      <c r="A32" s="1" t="s">
+    <row r="31" spans="1:5" outlineLevel="1">
+      <c r="A31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>6</v>
+      <c r="E31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" outlineLevel="2">
+      <c r="A32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="4">
+        <v>450</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:5" outlineLevel="2">
       <c r="A33" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B33" s="4">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" outlineLevel="2">
-      <c r="A34" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="4">
-        <v>360</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E33" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" outlineLevel="1">
+      <c r="A34" s="1" t="s">
         <v>118</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:5" outlineLevel="2">
       <c r="A35" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B35" s="4">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:5" outlineLevel="2">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B36" s="4">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:5" outlineLevel="1">
       <c r="A37" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>6</v>
@@ -1862,587 +1991,757 @@
         <v>6</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>6</v>
+        <v>130</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:5" outlineLevel="2">
       <c r="A38" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B38" s="4">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" outlineLevel="1">
-      <c r="A39" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>6</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" outlineLevel="2">
+      <c r="A39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="4">
+        <v>410</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5" outlineLevel="2">
       <c r="A40" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B40" s="4">
-        <v>355</v>
+        <v>410</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" outlineLevel="2">
-      <c r="A41" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="4">
-        <v>380</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>142</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" outlineLevel="1">
+      <c r="A41" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" outlineLevel="2">
       <c r="A42" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B42" s="4">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" outlineLevel="2">
-      <c r="A43" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="4">
-        <v>265</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D43" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="5" t="s">
+    </row>
+    <row r="43" spans="1:5" outlineLevel="1">
+      <c r="A43" s="1" t="s">
         <v>150</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:5" outlineLevel="2">
       <c r="A44" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" s="4">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:5" outlineLevel="2">
       <c r="A45" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="4">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D45" s="5" t="s">
         <v>157</v>
       </c>
+      <c r="D45" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="E45" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:5" outlineLevel="2">
       <c r="A46" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" s="4">
-        <v>265</v>
+        <v>360</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="3" t="s">
         <v>161</v>
       </c>
+      <c r="D46" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="E46" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:5" outlineLevel="2">
       <c r="A47" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" s="4">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="3" t="s">
         <v>165</v>
       </c>
+      <c r="D47" s="5" t="s">
+        <v>166</v>
+      </c>
       <c r="E47" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" outlineLevel="2">
-      <c r="A48" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B48" s="4">
-        <v>355</v>
-      </c>
-      <c r="C48" s="3" t="s">
+    </row>
+    <row r="48" spans="1:5" outlineLevel="1">
+      <c r="A48" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="B48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>170</v>
+      <c r="E48" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:5" outlineLevel="2">
       <c r="A49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" s="4">
+        <v>365</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B49" s="4">
-        <v>265</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E49" s="5" t="s">
+    </row>
+    <row r="50" spans="1:5" outlineLevel="1">
+      <c r="A50" s="1" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" outlineLevel="2">
-      <c r="A50" s="3" t="s">
+      <c r="B50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="4">
-        <v>265</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>178</v>
+      <c r="E50" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5" outlineLevel="2">
       <c r="A51" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B51" s="4">
         <v>355</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:5" outlineLevel="2">
       <c r="A52" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="4">
+        <v>380</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="B52" s="4">
-        <v>245</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:5" outlineLevel="2">
       <c r="A53" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B53" s="4">
+        <v>380</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B53" s="4">
-        <v>390</v>
-      </c>
-      <c r="C53" s="3" t="s">
+    </row>
+    <row r="54" spans="1:5" outlineLevel="2">
+      <c r="A54" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="B54" s="4">
+        <v>265</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" outlineLevel="1">
-      <c r="A54" s="1" t="s">
+      <c r="E54" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:5" outlineLevel="2">
       <c r="A55" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" s="4">
+        <v>385</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="4">
-        <v>449</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E55" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5" outlineLevel="2">
+      <c r="A56" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" outlineLevel="1">
-      <c r="A56" s="1" t="s">
+      <c r="B56" s="4">
+        <v>265</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>6</v>
+      <c r="D56" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:5" outlineLevel="2">
       <c r="A57" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B57" s="4">
-        <v>229</v>
+        <v>345</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:5" outlineLevel="2">
       <c r="A58" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B58" s="4">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:5" outlineLevel="2">
       <c r="A59" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B59" s="4">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:5" outlineLevel="2">
       <c r="A60" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B60" s="4">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:5" outlineLevel="2">
       <c r="A61" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B61" s="4">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" outlineLevel="1">
-      <c r="A62" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" outlineLevel="2">
-      <c r="A63" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B63" s="4">
-        <v>165</v>
-      </c>
-      <c r="C63" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D63" s="3" t="s">
+    </row>
+    <row r="62" spans="1:5" outlineLevel="2">
+      <c r="A62" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="B62" s="4">
+        <v>390</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>221</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" outlineLevel="1">
+      <c r="A63" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:5" outlineLevel="2">
       <c r="A64" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B64" s="4">
+        <v>449</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" outlineLevel="2">
-      <c r="A65" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="4">
+    </row>
+    <row r="65" spans="1:5" outlineLevel="1">
+      <c r="A65" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" outlineLevel="2">
+      <c r="A66" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B66" s="4">
+        <v>229</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" outlineLevel="2">
+      <c r="A67" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67" s="4">
+        <v>420</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" outlineLevel="2">
+      <c r="A68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" s="4">
+        <v>249</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" outlineLevel="2">
+      <c r="A69" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B69" s="4">
+        <v>249</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" outlineLevel="2">
+      <c r="A70" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B70" s="4">
+        <v>199</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" outlineLevel="2">
+      <c r="A71" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B71" s="4">
+        <v>199</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" outlineLevel="1">
+      <c r="A72" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" outlineLevel="2">
+      <c r="A73" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B73" s="4">
+        <v>165</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" outlineLevel="2">
+      <c r="A74" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B74" s="4">
+        <v>229</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" outlineLevel="2">
+      <c r="A75" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75" s="4">
         <v>170</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" outlineLevel="1">
-      <c r="A66" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B66" s="4">
+      <c r="C75" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" outlineLevel="1">
+      <c r="A76" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" s="4">
         <v>370</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" outlineLevel="1">
-      <c r="A67" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B67" s="4">
+      <c r="C76" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" outlineLevel="1">
+      <c r="A77" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" s="4">
         <v>390</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" outlineLevel="1">
-      <c r="A68" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B68" s="4">
+      <c r="C77" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" outlineLevel="1">
+      <c r="A78" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B78" s="4">
         <v>239</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C78" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" outlineLevel="1">
+      <c r="A79" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B79" s="4">
         <v>239</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" outlineLevel="1">
-      <c r="A69" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B69" s="4">
+      <c r="C79" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" outlineLevel="1">
+      <c r="A80" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B80" s="4">
         <v>239</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" outlineLevel="1">
-      <c r="A70" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B70" s="4">
-        <v>239</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" outlineLevel="1">
-      <c r="A71" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B71" s="4">
+      <c r="C80" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" outlineLevel="1">
+      <c r="A81" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B81" s="4">
         <v>219</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="C81" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>6</v>
       </c>
     </row>
